--- a/media/exports/reports/2025-11/program-cost.xlsx
+++ b/media/exports/reports/2025-11/program-cost.xlsx
@@ -24,45 +24,54 @@
     <numFmt numFmtId="164" formatCode="#,##0;[Red](#,##0);&quot;-&quot;"/>
     <numFmt numFmtId="165" formatCode="0.0%;[Red](0.0%);&quot;-&quot;"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <color theme="1"/>
+      <name val="Roboto"/>
       <sz val="11"/>
-      <scheme val="minor"/>
     </font>
     <font>
+      <name val="Roboto"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Roboto"/>
       <b val="1"/>
       <color rgb="0025342A"/>
       <sz val="14"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <i val="1"/>
       <color rgb="005F6F63"/>
       <sz val="9"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <b val="1"/>
       <color rgb="002F7A5D"/>
       <sz val="12"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <b val="1"/>
       <color rgb="0025342A"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <i val="1"/>
       <color rgb="005F6F63"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <b val="1"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <b val="1"/>
       <color rgb="002F7A5D"/>
     </font>
@@ -95,35 +104,35 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -885,8 +894,8 @@
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 Sample Community Services Ltd&amp;R&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;8 program-cost.xlsx&amp;C&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 program-cost.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -1482,8 +1491,8 @@
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 Sample Community Services Ltd&amp;R&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;8 program-cost.xlsx&amp;C&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 program-cost.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -1733,8 +1742,8 @@
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 Sample Community Services Ltd&amp;R&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;8 program-cost.xlsx&amp;C&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 program-cost.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/media/exports/reports/2025-11/program-cost.xlsx
+++ b/media/exports/reports/2025-11/program-cost.xlsx
@@ -12,7 +12,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Report'!$A$1:$D$64</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Workings'!$A$1:$B$67</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Data'!$9:$9</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Data'!$A$1:$F$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -210,6 +213,155 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="1100" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="25342A"/>
+                </a:solidFill>
+                <a:latin typeface="Roboto"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1100" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="25342A"/>
+                </a:solidFill>
+                <a:latin typeface="Roboto"/>
+              </a:rPr>
+              <a:t>Full cost of each program, November 2025</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+      <overlay val="0"/>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="bar"/>
+        <grouping val="clustered"/>
+        <varyColors val="0"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <v>$</v>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="0E9F6E"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="0E9F6E"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <invertIfNegative val="0"/>
+          <dLbls>
+            <numFmt formatCode="#,##0;(#,##0)"/>
+            <showLegendKey val="0"/>
+            <showVal val="1"/>
+            <showCatName val="0"/>
+            <showSerName val="0"/>
+            <showPercent val="0"/>
+          </dLbls>
+          <cat>
+            <numRef>
+              <f>'Report'!$A$10:$A$14</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Report'!$B$10:$B$14</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="60"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="maxMin"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="1"/>
+        <axPos val="l"/>
+        <numFmt formatCode="#,##0;(#,##0)" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>8</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="2070000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="program_cost_Data" displayName="program_cost_Data" ref="A9:F14" headerRowCount="1">
+  <autoFilter ref="A9:F14"/>
+  <tableColumns count="6">
+    <tableColumn id="1" name="Program"/>
+    <tableColumn id="2" name="Grant spending, Nov 2025"/>
+    <tableColumn id="3" name="Share"/>
+    <tableColumn id="4" name="Untied costs share"/>
+    <tableColumn id="5" name="Administration share"/>
+    <tableColumn id="6" name="Full cost"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -501,7 +653,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D60"/>
+  <dimension ref="A1:D66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -520,14 +672,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Sample Community Services Ltd · SAMPLE DATA (invented) · The Fourth Sheet</t>
+          <t>Sample Community Services Ltd · SAMPLE DATA (invented) · The Fourth Sheet · Made with Python (openpyxl)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: November 2025 · Data status: Oct 2025 locked · Nov 2025 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026)</t>
+          <t>Period: November 2025 · Data status: Oct 2025 locked · Nov 2025 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
         </is>
       </c>
     </row>
@@ -643,268 +795,275 @@
       </c>
     </row>
     <row r="15"/>
-    <row r="16">
-      <c r="A16" s="10" t="inlineStr">
-        <is>
-          <t>What it shows</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="45" customHeight="1">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>Housing support (2025) is the biggest program: $52,362 in November once its share of untied program costs and administration is added to $30,000 of grant spending. Shared costs add 74.5% on top of grant spending across all programs.</t>
-        </is>
-      </c>
-    </row>
+    <row r="16"/>
+    <row r="17"/>
     <row r="18"/>
-    <row r="19">
-      <c r="A19" s="10" t="inlineStr">
-        <is>
-          <t>What you'd do about it</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>The full cost (not just the grant line) is the number for renewal applications, where the funder lets you recover a share of overheads. Pick a program above to see it on its own.</t>
-        </is>
-      </c>
-    </row>
+    <row r="19"/>
+    <row r="20"/>
     <row r="21"/>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>What it shows</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="45" customHeight="1">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Housing support (2025) is the biggest program: $52,362 in November once its share of untied program costs and administration is added to $30,000 of grant spending. Shared costs add 74.5% on top of grant spending across all programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t>What you'd do about it</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>The full cost (not just the grant line) is the number for renewal applications, where the funder lets you recover a share of overheads. Pick a program above to see it on its own.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27"/>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
         <is>
           <t>Program: Housing support (2025)</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="10" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="10" t="inlineStr">
         <is>
           <t>What it shows</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="45" customHeight="1">
-      <c r="A24" s="3" t="inlineStr">
+    <row r="30" ht="45" customHeight="1">
+      <c r="A30" s="3" t="inlineStr">
         <is>
           <t>Housing support (2025) cost $52,362 in full in November: $30,000 paid by the State Housing Program grant, and $22,362 of shared costs no grant covers. It has spent 99.6% of its budget to date, with $29,100 left and 1 months to go.</t>
         </is>
       </c>
     </row>
-    <row r="25"/>
-    <row r="26">
-      <c r="A26" s="10" t="inlineStr">
+    <row r="31"/>
+    <row r="32">
+      <c r="A32" s="10" t="inlineStr">
         <is>
           <t>What you'd do about it</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="30" customHeight="1">
-      <c r="A27" s="3" t="inlineStr">
+    <row r="33" ht="30" customHeight="1">
+      <c r="A33" s="3" t="inlineStr">
         <is>
           <t>The full cost is $52,362 a month; $22,362 of it is shared cost the grant doesn't pay for. Worth asking for as much of it as the funder allows at renewal.</t>
         </is>
       </c>
     </row>
-    <row r="28"/>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
+    <row r="34"/>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>Program: Youth outreach</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="10" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="10" t="inlineStr">
         <is>
           <t>What it shows</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="45" customHeight="1">
-      <c r="A31" s="3" t="inlineStr">
+    <row r="37" ht="45" customHeight="1">
+      <c r="A37" s="3" t="inlineStr">
         <is>
           <t>Youth outreach cost $36,791 in full in November: $21,079 paid by the State Department of Families grant, and $15,712 of shared costs no grant covers. It has spent 99.0% of its budget to date, with $380,952 left and 19 months to go.</t>
         </is>
       </c>
     </row>
-    <row r="32"/>
-    <row r="33">
-      <c r="A33" s="10" t="inlineStr">
+    <row r="38"/>
+    <row r="39">
+      <c r="A39" s="10" t="inlineStr">
         <is>
           <t>What you'd do about it</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="30" customHeight="1">
-      <c r="A34" s="3" t="inlineStr">
+    <row r="40" ht="30" customHeight="1">
+      <c r="A40" s="3" t="inlineStr">
         <is>
           <t>The full cost is $36,791 a month; $15,712 of it is shared cost the grant doesn't pay for. Worth asking for as much of it as the funder allows at renewal.</t>
         </is>
       </c>
     </row>
-    <row r="35"/>
-    <row r="36">
-      <c r="A36" s="4" t="inlineStr">
+    <row r="41"/>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
         <is>
           <t>Program: Emergency relief</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="10" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="10" t="inlineStr">
         <is>
           <t>What it shows</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="45" customHeight="1">
-      <c r="A38" s="3" t="inlineStr">
+    <row r="44" ht="45" customHeight="1">
+      <c r="A44" s="3" t="inlineStr">
         <is>
           <t>Emergency relief cost $19,898 in full in November: $11,400 paid by the Federal community grant grant, and $8,498 of shared costs no grant covers. It has spent 99.7% of its budget to date (spending before October 2024 taken at budget), with $12,900 left and 1 months to go.</t>
         </is>
       </c>
     </row>
-    <row r="39"/>
-    <row r="40">
-      <c r="A40" s="10" t="inlineStr">
+    <row r="45"/>
+    <row r="46">
+      <c r="A46" s="10" t="inlineStr">
         <is>
           <t>What you'd do about it</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="30" customHeight="1">
-      <c r="A41" s="3" t="inlineStr">
+    <row r="47" ht="30" customHeight="1">
+      <c r="A47" s="3" t="inlineStr">
         <is>
           <t>The full cost is $19,898 a month; $8,498 of it is shared cost the grant doesn't pay for. Worth asking for as much of it as the funder allows at renewal.</t>
         </is>
       </c>
     </row>
-    <row r="42"/>
-    <row r="43">
-      <c r="A43" s="4" t="inlineStr">
+    <row r="48"/>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
         <is>
           <t>Program: Digital literacy</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="10" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="10" t="inlineStr">
         <is>
           <t>What it shows</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="45" customHeight="1">
-      <c r="A45" s="3" t="inlineStr">
+    <row r="51" ht="45" customHeight="1">
+      <c r="A51" s="3" t="inlineStr">
         <is>
           <t>Digital literacy cost $8,003 in full in November: $4,585 paid by the Philanthropic foundation grant, and $3,418 of shared costs no grant covers. It has spent 97.5% of its budget to date, with $80,255 left and 16 months to go.</t>
         </is>
       </c>
     </row>
-    <row r="46"/>
-    <row r="47">
-      <c r="A47" s="10" t="inlineStr">
+    <row r="52"/>
+    <row r="53">
+      <c r="A53" s="10" t="inlineStr">
         <is>
           <t>What you'd do about it</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="30" customHeight="1">
-      <c r="A48" s="3" t="inlineStr">
+    <row r="54" ht="30" customHeight="1">
+      <c r="A54" s="3" t="inlineStr">
         <is>
           <t>The full cost is $8,003 a month; $3,418 of it is shared cost the grant doesn't pay for. Worth asking for as much of it as the funder allows at renewal.</t>
         </is>
       </c>
     </row>
-    <row r="49"/>
-    <row r="50">
-      <c r="A50" s="4" t="inlineStr">
+    <row r="55"/>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
         <is>
           <t>Program: Community meals (2025-26)</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="10" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="10" t="inlineStr">
         <is>
           <t>What it shows</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="45" customHeight="1">
-      <c r="A52" s="3" t="inlineStr">
+    <row r="58" ht="45" customHeight="1">
+      <c r="A58" s="3" t="inlineStr">
         <is>
           <t>Community meals (2025-26) cost $5,411 in full in November: $3,100 paid by the Local council community grant grant, and $2,311 of shared costs no grant covers. It has spent 93.8% of its budget to date, with $26,800 left and 7 months to go.</t>
         </is>
       </c>
     </row>
-    <row r="53"/>
-    <row r="54">
-      <c r="A54" s="10" t="inlineStr">
+    <row r="59"/>
+    <row r="60">
+      <c r="A60" s="10" t="inlineStr">
         <is>
           <t>What you'd do about it</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="30" customHeight="1">
-      <c r="A55" s="3" t="inlineStr">
+    <row r="61" ht="30" customHeight="1">
+      <c r="A61" s="3" t="inlineStr">
         <is>
           <t>The full cost is $5,411 a month; $2,311 of it is shared cost the grant doesn't pay for. Worth asking for as much of it as the funder allows at renewal.</t>
         </is>
       </c>
     </row>
-    <row r="56"/>
-    <row r="57">
-      <c r="A57" s="4" t="inlineStr">
+    <row r="62"/>
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr">
         <is>
           <t>Every program at once</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="11" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="11" t="inlineStr">
         <is>
           <t>Grant spending, by month: every month is on the Data sheet.</t>
         </is>
       </c>
     </row>
-    <row r="59"/>
-    <row r="60"/>
+    <row r="65"/>
+    <row r="66"/>
   </sheetData>
   <mergeCells count="13">
     <mergeCell ref="A5:D5"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A45:D45"/>
-    <mergeCell ref="A27:D27"/>
-    <mergeCell ref="A31:D31"/>
-    <mergeCell ref="A34:D34"/>
-    <mergeCell ref="A48:D48"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="A38:D38"/>
-    <mergeCell ref="A55:D55"/>
-    <mergeCell ref="A52:D52"/>
-    <mergeCell ref="A24:D24"/>
-    <mergeCell ref="A41:D41"/>
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="A40:D40"/>
+    <mergeCell ref="A61:D61"/>
+    <mergeCell ref="A58:D58"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A54:D54"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A51:D51"/>
+    <mergeCell ref="A47:D47"/>
+    <mergeCell ref="A44:D44"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 program-cost.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 program-cost.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
   <rowBreaks count="2" manualBreakCount="2">
-    <brk id="22" min="0" max="16383" man="1"/>
-    <brk id="43" min="0" max="16383" man="1"/>
+    <brk id="27" min="0" max="16383" man="1"/>
+    <brk id="49" min="0" max="16383" man="1"/>
   </rowBreaks>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -933,14 +1092,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Sample Community Services Ltd · SAMPLE DATA (invented) · The Fourth Sheet</t>
+          <t>Sample Community Services Ltd · SAMPLE DATA (invented) · The Fourth Sheet · Made with Python (openpyxl)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: November 2025 · Data status: Oct 2025 locked · Nov 2025 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026)</t>
+          <t>Period: November 2025 · Data status: Oct 2025 locked · Nov 2025 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
         </is>
       </c>
     </row>
@@ -1492,7 +1651,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 program-cost.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 program-cost.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -1532,14 +1691,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Sample Community Services Ltd · SAMPLE DATA (invented) · The Fourth Sheet</t>
+          <t>Sample Community Services Ltd · SAMPLE DATA (invented) · The Fourth Sheet · Made with Python (openpyxl)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: November 2025 · Data status: Oct 2025 locked · Nov 2025 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026)</t>
+          <t>Period: November 2025 · Data status: Oct 2025 locked · Nov 2025 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
         </is>
       </c>
     </row>
@@ -1743,11 +1902,14 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 program-cost.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 program-cost.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/media/exports/reports/2025-11/program-cost.xlsx
+++ b/media/exports/reports/2025-11/program-cost.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Report'!$A$1:$D$64</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Report'!$A$1:$D$65</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Workings'!$A$1:$B$67</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Data'!$9:$9</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Data'!$A$1:$F$14</definedName>
@@ -51,13 +51,13 @@
     <font>
       <name val="Roboto"/>
       <b val="1"/>
-      <color rgb="002F7A5D"/>
-      <sz val="12"/>
+      <color rgb="0025342A"/>
     </font>
     <font>
       <name val="Roboto"/>
       <b val="1"/>
-      <color rgb="0025342A"/>
+      <color rgb="002F7A5D"/>
+      <sz val="12"/>
     </font>
     <font>
       <name val="Roboto"/>
@@ -109,15 +109,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -279,12 +282,12 @@
           </dLbls>
           <cat>
             <numRef>
-              <f>'Report'!$A$10:$A$14</f>
+              <f>'Report'!$A$11:$A$15</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Report'!$B$10:$B$14</f>
+              <f>'Report'!$B$11:$B$15</f>
             </numRef>
           </val>
         </ser>
@@ -328,7 +331,7 @@
     <from>
       <col>5</col>
       <colOff>0</colOff>
-      <row>8</row>
+      <row>9</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5400000" cy="2070000"/>
@@ -653,7 +656,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D66"/>
+  <dimension ref="A1:D67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -679,7 +682,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: November 2025 · Data status: Oct 2025 locked · Nov 2025 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
+          <t>Period: November 2025 · Data status: Oct 2025 locked · Nov 2025 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 10 Oct 2026, 9:55pm</t>
         </is>
       </c>
     </row>
@@ -687,381 +690,390 @@
     <row r="5" ht="32" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
+          <t>In short: Housing support (2025) costs $52,362 in full in November: $22,362 more than its grant spending, once its share of shared costs is added.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
           <t>Each program's full cost: what its grant pays for, plus its fair share of the costs no single grant covers (untied program costs and administration, shared by grant spending). Pick a program and every chart and note follows it.</t>
         </is>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>Program: All programs</t>
-        </is>
-      </c>
-    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
+          <t>Program: All programs</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
           <t>Full cost of each program, November 2025</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="6" t="inlineStr"/>
-      <c r="B9" s="7" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr"/>
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>$</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>% of total</t>
         </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Housing support (2025)</t>
-        </is>
-      </c>
-      <c r="B10" s="8">
-        <f>Workings!B15</f>
-        <v/>
-      </c>
-      <c r="C10" s="9">
-        <f>Workings!B10</f>
-        <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Youth outreach</t>
-        </is>
-      </c>
-      <c r="B11" s="8">
-        <f>Workings!B28</f>
-        <v/>
-      </c>
-      <c r="C11" s="9">
-        <f>Workings!B23</f>
+          <t>Housing support (2025)</t>
+        </is>
+      </c>
+      <c r="B11" s="9">
+        <f>Workings!B15</f>
+        <v/>
+      </c>
+      <c r="C11" s="10">
+        <f>Workings!B10</f>
         <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Emergency relief</t>
-        </is>
-      </c>
-      <c r="B12" s="8">
-        <f>Workings!B41</f>
-        <v/>
-      </c>
-      <c r="C12" s="9">
-        <f>Workings!B36</f>
+          <t>Youth outreach</t>
+        </is>
+      </c>
+      <c r="B12" s="9">
+        <f>Workings!B28</f>
+        <v/>
+      </c>
+      <c r="C12" s="10">
+        <f>Workings!B23</f>
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Digital literacy</t>
-        </is>
-      </c>
-      <c r="B13" s="8">
-        <f>Workings!B54</f>
-        <v/>
-      </c>
-      <c r="C13" s="9">
-        <f>Workings!B49</f>
+          <t>Emergency relief</t>
+        </is>
+      </c>
+      <c r="B13" s="9">
+        <f>Workings!B41</f>
+        <v/>
+      </c>
+      <c r="C13" s="10">
+        <f>Workings!B36</f>
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>Digital literacy</t>
+        </is>
+      </c>
+      <c r="B14" s="9">
+        <f>Workings!B54</f>
+        <v/>
+      </c>
+      <c r="C14" s="10">
+        <f>Workings!B49</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>Community meals (2025-26)</t>
         </is>
       </c>
-      <c r="B14" s="8">
+      <c r="B15" s="9">
         <f>Workings!B67</f>
         <v/>
       </c>
-      <c r="C14" s="9">
+      <c r="C15" s="10">
         <f>Workings!B62</f>
         <v/>
       </c>
     </row>
-    <row r="15"/>
     <row r="16"/>
     <row r="17"/>
     <row r="18"/>
     <row r="19"/>
     <row r="20"/>
     <row r="21"/>
-    <row r="22">
-      <c r="A22" s="10" t="inlineStr">
+    <row r="22"/>
+    <row r="23">
+      <c r="A23" s="11" t="inlineStr">
         <is>
           <t>What it shows</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="45" customHeight="1">
-      <c r="A23" s="3" t="inlineStr">
+    <row r="24" ht="45" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>Housing support (2025) is the biggest program: $52,362 in November once its share of untied program costs and administration is added to $30,000 of grant spending. Shared costs add 74.5% on top of grant spending across all programs.</t>
         </is>
       </c>
     </row>
-    <row r="24"/>
-    <row r="25">
-      <c r="A25" s="10" t="inlineStr">
+    <row r="25"/>
+    <row r="26">
+      <c r="A26" s="11" t="inlineStr">
         <is>
           <t>What you'd do about it</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="30" customHeight="1">
-      <c r="A26" s="3" t="inlineStr">
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t>The full cost (not just the grant line) is the number for renewal applications, where the funder lets you recover a share of overheads. Pick a program above to see it on its own.</t>
         </is>
       </c>
     </row>
-    <row r="27"/>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr">
+    <row r="28"/>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>Program: Housing support (2025)</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="10" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="11" t="inlineStr">
         <is>
           <t>What it shows</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="45" customHeight="1">
-      <c r="A30" s="3" t="inlineStr">
+    <row r="31" ht="45" customHeight="1">
+      <c r="A31" s="4" t="inlineStr">
         <is>
           <t>Housing support (2025) cost $52,362 in full in November: $30,000 paid by the State Housing Program grant, and $22,362 of shared costs no grant covers. It has spent 99.6% of its budget to date, with $29,100 left and 1 months to go.</t>
         </is>
       </c>
     </row>
-    <row r="31"/>
-    <row r="32">
-      <c r="A32" s="10" t="inlineStr">
+    <row r="32"/>
+    <row r="33">
+      <c r="A33" s="11" t="inlineStr">
         <is>
           <t>What you'd do about it</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="30" customHeight="1">
-      <c r="A33" s="3" t="inlineStr">
+    <row r="34" ht="30" customHeight="1">
+      <c r="A34" s="4" t="inlineStr">
         <is>
           <t>The full cost is $52,362 a month; $22,362 of it is shared cost the grant doesn't pay for. Worth asking for as much of it as the funder allows at renewal.</t>
         </is>
       </c>
     </row>
-    <row r="34"/>
-    <row r="35">
-      <c r="A35" s="4" t="inlineStr">
+    <row r="35"/>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
         <is>
           <t>Program: Youth outreach</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="10" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="11" t="inlineStr">
         <is>
           <t>What it shows</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="45" customHeight="1">
-      <c r="A37" s="3" t="inlineStr">
+    <row r="38" ht="45" customHeight="1">
+      <c r="A38" s="4" t="inlineStr">
         <is>
           <t>Youth outreach cost $36,791 in full in November: $21,079 paid by the State Department of Families grant, and $15,712 of shared costs no grant covers. It has spent 99.0% of its budget to date, with $380,952 left and 19 months to go.</t>
         </is>
       </c>
     </row>
-    <row r="38"/>
-    <row r="39">
-      <c r="A39" s="10" t="inlineStr">
+    <row r="39"/>
+    <row r="40">
+      <c r="A40" s="11" t="inlineStr">
         <is>
           <t>What you'd do about it</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="30" customHeight="1">
-      <c r="A40" s="3" t="inlineStr">
+    <row r="41" ht="30" customHeight="1">
+      <c r="A41" s="4" t="inlineStr">
         <is>
           <t>The full cost is $36,791 a month; $15,712 of it is shared cost the grant doesn't pay for. Worth asking for as much of it as the funder allows at renewal.</t>
         </is>
       </c>
     </row>
-    <row r="41"/>
-    <row r="42">
-      <c r="A42" s="4" t="inlineStr">
+    <row r="42"/>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
         <is>
           <t>Program: Emergency relief</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="10" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="11" t="inlineStr">
         <is>
           <t>What it shows</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="45" customHeight="1">
-      <c r="A44" s="3" t="inlineStr">
+    <row r="45" ht="45" customHeight="1">
+      <c r="A45" s="4" t="inlineStr">
         <is>
           <t>Emergency relief cost $19,898 in full in November: $11,400 paid by the Federal community grant grant, and $8,498 of shared costs no grant covers. It has spent 99.7% of its budget to date (spending before October 2024 taken at budget), with $12,900 left and 1 months to go.</t>
         </is>
       </c>
     </row>
-    <row r="45"/>
-    <row r="46">
-      <c r="A46" s="10" t="inlineStr">
+    <row r="46"/>
+    <row r="47">
+      <c r="A47" s="11" t="inlineStr">
         <is>
           <t>What you'd do about it</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="30" customHeight="1">
-      <c r="A47" s="3" t="inlineStr">
+    <row r="48" ht="30" customHeight="1">
+      <c r="A48" s="4" t="inlineStr">
         <is>
           <t>The full cost is $19,898 a month; $8,498 of it is shared cost the grant doesn't pay for. Worth asking for as much of it as the funder allows at renewal.</t>
         </is>
       </c>
     </row>
-    <row r="48"/>
-    <row r="49">
-      <c r="A49" s="4" t="inlineStr">
+    <row r="49"/>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
         <is>
           <t>Program: Digital literacy</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="10" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="11" t="inlineStr">
         <is>
           <t>What it shows</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="45" customHeight="1">
-      <c r="A51" s="3" t="inlineStr">
+    <row r="52" ht="45" customHeight="1">
+      <c r="A52" s="4" t="inlineStr">
         <is>
           <t>Digital literacy cost $8,003 in full in November: $4,585 paid by the Philanthropic foundation grant, and $3,418 of shared costs no grant covers. It has spent 97.5% of its budget to date, with $80,255 left and 16 months to go.</t>
         </is>
       </c>
     </row>
-    <row r="52"/>
-    <row r="53">
-      <c r="A53" s="10" t="inlineStr">
+    <row r="53"/>
+    <row r="54">
+      <c r="A54" s="11" t="inlineStr">
         <is>
           <t>What you'd do about it</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="30" customHeight="1">
-      <c r="A54" s="3" t="inlineStr">
+    <row r="55" ht="30" customHeight="1">
+      <c r="A55" s="4" t="inlineStr">
         <is>
           <t>The full cost is $8,003 a month; $3,418 of it is shared cost the grant doesn't pay for. Worth asking for as much of it as the funder allows at renewal.</t>
         </is>
       </c>
     </row>
-    <row r="55"/>
-    <row r="56">
-      <c r="A56" s="4" t="inlineStr">
+    <row r="56"/>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
         <is>
           <t>Program: Community meals (2025-26)</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="10" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="11" t="inlineStr">
         <is>
           <t>What it shows</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="45" customHeight="1">
-      <c r="A58" s="3" t="inlineStr">
+    <row r="59" ht="45" customHeight="1">
+      <c r="A59" s="4" t="inlineStr">
         <is>
           <t>Community meals (2025-26) cost $5,411 in full in November: $3,100 paid by the Local council community grant grant, and $2,311 of shared costs no grant covers. It has spent 93.8% of its budget to date, with $26,800 left and 7 months to go.</t>
         </is>
       </c>
     </row>
-    <row r="59"/>
-    <row r="60">
-      <c r="A60" s="10" t="inlineStr">
+    <row r="60"/>
+    <row r="61">
+      <c r="A61" s="11" t="inlineStr">
         <is>
           <t>What you'd do about it</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="30" customHeight="1">
-      <c r="A61" s="3" t="inlineStr">
+    <row r="62" ht="30" customHeight="1">
+      <c r="A62" s="4" t="inlineStr">
         <is>
           <t>The full cost is $5,411 a month; $2,311 of it is shared cost the grant doesn't pay for. Worth asking for as much of it as the funder allows at renewal.</t>
         </is>
       </c>
     </row>
-    <row r="62"/>
-    <row r="63">
-      <c r="A63" s="4" t="inlineStr">
+    <row r="63"/>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
         <is>
           <t>Every program at once</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="11" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="12" t="inlineStr">
         <is>
           <t>Grant spending, by month: every month is on the Data sheet.</t>
         </is>
       </c>
     </row>
-    <row r="65"/>
     <row r="66"/>
+    <row r="67"/>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="14">
     <mergeCell ref="A5:D5"/>
-    <mergeCell ref="A23:D23"/>
-    <mergeCell ref="A37:D37"/>
-    <mergeCell ref="A40:D40"/>
-    <mergeCell ref="A61:D61"/>
-    <mergeCell ref="A58:D58"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="A30:D30"/>
-    <mergeCell ref="A54:D54"/>
-    <mergeCell ref="A33:D33"/>
-    <mergeCell ref="A51:D51"/>
-    <mergeCell ref="A47:D47"/>
-    <mergeCell ref="A44:D44"/>
+    <mergeCell ref="A45:D45"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A48:D48"/>
+    <mergeCell ref="A62:D62"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="A55:D55"/>
+    <mergeCell ref="A52:D52"/>
+    <mergeCell ref="A59:D59"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="A41:D41"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 program-cost.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 program-cost.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 10 Oct 2026, 9:55pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
-  <rowBreaks count="2" manualBreakCount="2">
-    <brk id="27" min="0" max="16383" man="1"/>
-    <brk id="49" min="0" max="16383" man="1"/>
+  <rowBreaks count="3" manualBreakCount="3">
+    <brk id="22" min="0" max="16383" man="1"/>
+    <brk id="43" min="0" max="16383" man="1"/>
+    <brk id="63" min="0" max="16383" man="1"/>
   </rowBreaks>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
@@ -1099,28 +1111,28 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: November 2025 · Data status: Oct 2025 locked · Nov 2025 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
+          <t>Period: November 2025 · Data status: Oct 2025 locked · Nov 2025 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 10 Oct 2026, 9:55pm</t>
         </is>
       </c>
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Housing support (2025): full cost, November</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Grant spending + its share of untied program costs and administration (shared by grant spending)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr"/>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr"/>
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>Nov 2025</t>
         </is>
@@ -1132,7 +1144,7 @@
           <t>Grant spending on the program</t>
         </is>
       </c>
-      <c r="B8" s="12" t="n">
+      <c r="B8" s="13" t="n">
         <v>30000</v>
       </c>
     </row>
@@ -1142,7 +1154,7 @@
           <t>All grant-funded program spending</t>
         </is>
       </c>
-      <c r="B9" s="12" t="n">
+      <c r="B9" s="13" t="n">
         <v>70164</v>
       </c>
     </row>
@@ -1152,7 +1164,7 @@
           <t>Share of program spending</t>
         </is>
       </c>
-      <c r="B10" s="13">
+      <c r="B10" s="14">
         <f>B8/B9</f>
         <v/>
       </c>
@@ -1163,7 +1175,7 @@
           <t>Untied program costs (all programs)</t>
         </is>
       </c>
-      <c r="B11" s="12" t="n">
+      <c r="B11" s="13" t="n">
         <v>16900</v>
       </c>
     </row>
@@ -1173,7 +1185,7 @@
           <t>Share of untied program costs</t>
         </is>
       </c>
-      <c r="B12" s="12">
+      <c r="B12" s="13">
         <f>B10*B11</f>
         <v/>
       </c>
@@ -1184,7 +1196,7 @@
           <t>Administration (all)</t>
         </is>
       </c>
-      <c r="B13" s="12" t="n">
+      <c r="B13" s="13" t="n">
         <v>35400</v>
       </c>
     </row>
@@ -1194,18 +1206,18 @@
           <t>Share of administration</t>
         </is>
       </c>
-      <c r="B14" s="12">
+      <c r="B14" s="13">
         <f>B10*B13</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="14" t="inlineStr">
+      <c r="A15" s="15" t="inlineStr">
         <is>
           <t>Full cost of the program</t>
         </is>
       </c>
-      <c r="B15" s="15">
+      <c r="B15" s="16">
         <f>B8+B12+B14</f>
         <v/>
       </c>
@@ -1213,22 +1225,22 @@
     <row r="16"/>
     <row r="17"/>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>Youth outreach: full cost, November</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="11" t="inlineStr">
+      <c r="A19" s="12" t="inlineStr">
         <is>
           <t>Grant spending + its share of untied program costs and administration (shared by grant spending)</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="6" t="inlineStr"/>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="A20" s="7" t="inlineStr"/>
+      <c r="B20" s="8" t="inlineStr">
         <is>
           <t>Nov 2025</t>
         </is>
@@ -1240,7 +1252,7 @@
           <t>Grant spending on the program</t>
         </is>
       </c>
-      <c r="B21" s="12" t="n">
+      <c r="B21" s="13" t="n">
         <v>21079</v>
       </c>
     </row>
@@ -1250,7 +1262,7 @@
           <t>All grant-funded program spending</t>
         </is>
       </c>
-      <c r="B22" s="12" t="n">
+      <c r="B22" s="13" t="n">
         <v>70164</v>
       </c>
     </row>
@@ -1260,7 +1272,7 @@
           <t>Share of program spending</t>
         </is>
       </c>
-      <c r="B23" s="13">
+      <c r="B23" s="14">
         <f>B21/B22</f>
         <v/>
       </c>
@@ -1271,7 +1283,7 @@
           <t>Untied program costs (all programs)</t>
         </is>
       </c>
-      <c r="B24" s="12" t="n">
+      <c r="B24" s="13" t="n">
         <v>16900</v>
       </c>
     </row>
@@ -1281,7 +1293,7 @@
           <t>Share of untied program costs</t>
         </is>
       </c>
-      <c r="B25" s="12">
+      <c r="B25" s="13">
         <f>B23*B24</f>
         <v/>
       </c>
@@ -1292,7 +1304,7 @@
           <t>Administration (all)</t>
         </is>
       </c>
-      <c r="B26" s="12" t="n">
+      <c r="B26" s="13" t="n">
         <v>35400</v>
       </c>
     </row>
@@ -1302,18 +1314,18 @@
           <t>Share of administration</t>
         </is>
       </c>
-      <c r="B27" s="12">
+      <c r="B27" s="13">
         <f>B23*B26</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="14" t="inlineStr">
+      <c r="A28" s="15" t="inlineStr">
         <is>
           <t>Full cost of the program</t>
         </is>
       </c>
-      <c r="B28" s="15">
+      <c r="B28" s="16">
         <f>B21+B25+B27</f>
         <v/>
       </c>
@@ -1321,22 +1333,22 @@
     <row r="29"/>
     <row r="30"/>
     <row r="31">
-      <c r="A31" s="4" t="inlineStr">
+      <c r="A31" s="5" t="inlineStr">
         <is>
           <t>Emergency relief: full cost, November</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="11" t="inlineStr">
+      <c r="A32" s="12" t="inlineStr">
         <is>
           <t>Grant spending + its share of untied program costs and administration (shared by grant spending)</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="6" t="inlineStr"/>
-      <c r="B33" s="7" t="inlineStr">
+      <c r="A33" s="7" t="inlineStr"/>
+      <c r="B33" s="8" t="inlineStr">
         <is>
           <t>Nov 2025</t>
         </is>
@@ -1348,7 +1360,7 @@
           <t>Grant spending on the program</t>
         </is>
       </c>
-      <c r="B34" s="12" t="n">
+      <c r="B34" s="13" t="n">
         <v>11400</v>
       </c>
     </row>
@@ -1358,7 +1370,7 @@
           <t>All grant-funded program spending</t>
         </is>
       </c>
-      <c r="B35" s="12" t="n">
+      <c r="B35" s="13" t="n">
         <v>70164</v>
       </c>
     </row>
@@ -1368,7 +1380,7 @@
           <t>Share of program spending</t>
         </is>
       </c>
-      <c r="B36" s="13">
+      <c r="B36" s="14">
         <f>B34/B35</f>
         <v/>
       </c>
@@ -1379,7 +1391,7 @@
           <t>Untied program costs (all programs)</t>
         </is>
       </c>
-      <c r="B37" s="12" t="n">
+      <c r="B37" s="13" t="n">
         <v>16900</v>
       </c>
     </row>
@@ -1389,7 +1401,7 @@
           <t>Share of untied program costs</t>
         </is>
       </c>
-      <c r="B38" s="12">
+      <c r="B38" s="13">
         <f>B36*B37</f>
         <v/>
       </c>
@@ -1400,7 +1412,7 @@
           <t>Administration (all)</t>
         </is>
       </c>
-      <c r="B39" s="12" t="n">
+      <c r="B39" s="13" t="n">
         <v>35400</v>
       </c>
     </row>
@@ -1410,18 +1422,18 @@
           <t>Share of administration</t>
         </is>
       </c>
-      <c r="B40" s="12">
+      <c r="B40" s="13">
         <f>B36*B39</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="14" t="inlineStr">
+      <c r="A41" s="15" t="inlineStr">
         <is>
           <t>Full cost of the program</t>
         </is>
       </c>
-      <c r="B41" s="15">
+      <c r="B41" s="16">
         <f>B34+B38+B40</f>
         <v/>
       </c>
@@ -1429,22 +1441,22 @@
     <row r="42"/>
     <row r="43"/>
     <row r="44">
-      <c r="A44" s="4" t="inlineStr">
+      <c r="A44" s="5" t="inlineStr">
         <is>
           <t>Digital literacy: full cost, November</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="11" t="inlineStr">
+      <c r="A45" s="12" t="inlineStr">
         <is>
           <t>Grant spending + its share of untied program costs and administration (shared by grant spending)</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="6" t="inlineStr"/>
-      <c r="B46" s="7" t="inlineStr">
+      <c r="A46" s="7" t="inlineStr"/>
+      <c r="B46" s="8" t="inlineStr">
         <is>
           <t>Nov 2025</t>
         </is>
@@ -1456,7 +1468,7 @@
           <t>Grant spending on the program</t>
         </is>
       </c>
-      <c r="B47" s="12" t="n">
+      <c r="B47" s="13" t="n">
         <v>4585</v>
       </c>
     </row>
@@ -1466,7 +1478,7 @@
           <t>All grant-funded program spending</t>
         </is>
       </c>
-      <c r="B48" s="12" t="n">
+      <c r="B48" s="13" t="n">
         <v>70164</v>
       </c>
     </row>
@@ -1476,7 +1488,7 @@
           <t>Share of program spending</t>
         </is>
       </c>
-      <c r="B49" s="13">
+      <c r="B49" s="14">
         <f>B47/B48</f>
         <v/>
       </c>
@@ -1487,7 +1499,7 @@
           <t>Untied program costs (all programs)</t>
         </is>
       </c>
-      <c r="B50" s="12" t="n">
+      <c r="B50" s="13" t="n">
         <v>16900</v>
       </c>
     </row>
@@ -1497,7 +1509,7 @@
           <t>Share of untied program costs</t>
         </is>
       </c>
-      <c r="B51" s="12">
+      <c r="B51" s="13">
         <f>B49*B50</f>
         <v/>
       </c>
@@ -1508,7 +1520,7 @@
           <t>Administration (all)</t>
         </is>
       </c>
-      <c r="B52" s="12" t="n">
+      <c r="B52" s="13" t="n">
         <v>35400</v>
       </c>
     </row>
@@ -1518,18 +1530,18 @@
           <t>Share of administration</t>
         </is>
       </c>
-      <c r="B53" s="12">
+      <c r="B53" s="13">
         <f>B49*B52</f>
         <v/>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="14" t="inlineStr">
+      <c r="A54" s="15" t="inlineStr">
         <is>
           <t>Full cost of the program</t>
         </is>
       </c>
-      <c r="B54" s="15">
+      <c r="B54" s="16">
         <f>B47+B51+B53</f>
         <v/>
       </c>
@@ -1537,22 +1549,22 @@
     <row r="55"/>
     <row r="56"/>
     <row r="57">
-      <c r="A57" s="4" t="inlineStr">
+      <c r="A57" s="5" t="inlineStr">
         <is>
           <t>Community meals (2025-26): full cost, November</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="11" t="inlineStr">
+      <c r="A58" s="12" t="inlineStr">
         <is>
           <t>Grant spending + its share of untied program costs and administration (shared by grant spending)</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="6" t="inlineStr"/>
-      <c r="B59" s="7" t="inlineStr">
+      <c r="A59" s="7" t="inlineStr"/>
+      <c r="B59" s="8" t="inlineStr">
         <is>
           <t>Nov 2025</t>
         </is>
@@ -1564,7 +1576,7 @@
           <t>Grant spending on the program</t>
         </is>
       </c>
-      <c r="B60" s="12" t="n">
+      <c r="B60" s="13" t="n">
         <v>3100</v>
       </c>
     </row>
@@ -1574,7 +1586,7 @@
           <t>All grant-funded program spending</t>
         </is>
       </c>
-      <c r="B61" s="12" t="n">
+      <c r="B61" s="13" t="n">
         <v>70164</v>
       </c>
     </row>
@@ -1584,7 +1596,7 @@
           <t>Share of program spending</t>
         </is>
       </c>
-      <c r="B62" s="13">
+      <c r="B62" s="14">
         <f>B60/B61</f>
         <v/>
       </c>
@@ -1595,7 +1607,7 @@
           <t>Untied program costs (all programs)</t>
         </is>
       </c>
-      <c r="B63" s="12" t="n">
+      <c r="B63" s="13" t="n">
         <v>16900</v>
       </c>
     </row>
@@ -1605,7 +1617,7 @@
           <t>Share of untied program costs</t>
         </is>
       </c>
-      <c r="B64" s="12">
+      <c r="B64" s="13">
         <f>B62*B63</f>
         <v/>
       </c>
@@ -1616,7 +1628,7 @@
           <t>Administration (all)</t>
         </is>
       </c>
-      <c r="B65" s="12" t="n">
+      <c r="B65" s="13" t="n">
         <v>35400</v>
       </c>
     </row>
@@ -1626,18 +1638,18 @@
           <t>Share of administration</t>
         </is>
       </c>
-      <c r="B66" s="12">
+      <c r="B66" s="13">
         <f>B62*B65</f>
         <v/>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="14" t="inlineStr">
+      <c r="A67" s="15" t="inlineStr">
         <is>
           <t>Full cost of the program</t>
         </is>
       </c>
-      <c r="B67" s="15">
+      <c r="B67" s="16">
         <f>B60+B64+B66</f>
         <v/>
       </c>
@@ -1651,7 +1663,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 program-cost.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 program-cost.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 10 Oct 2026, 9:55pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -1698,7 +1710,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: November 2025 · Data status: Oct 2025 locked · Nov 2025 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
+          <t>Period: November 2025 · Data status: Oct 2025 locked · Nov 2025 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 10 Oct 2026, 9:55pm</t>
         </is>
       </c>
     </row>
@@ -1709,7 +1721,7 @@
           <t>All grant-funded program spending, November 2025</t>
         </is>
       </c>
-      <c r="B5" s="8" t="n">
+      <c r="B5" s="9" t="n">
         <v>70164</v>
       </c>
     </row>
@@ -1719,7 +1731,7 @@
           <t>Untied program costs, November 2025 (all programs)</t>
         </is>
       </c>
-      <c r="B6" s="8" t="n">
+      <c r="B6" s="9" t="n">
         <v>16900</v>
       </c>
     </row>
@@ -1729,169 +1741,169 @@
           <t>Administration, November 2025 (all)</t>
         </is>
       </c>
-      <c r="B7" s="8" t="n">
+      <c r="B7" s="9" t="n">
         <v>35400</v>
       </c>
     </row>
     <row r="8"/>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>Program</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>Grant spending, Nov 2025</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>Share</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="D9" s="8" t="inlineStr">
         <is>
           <t>Untied costs share</t>
         </is>
       </c>
-      <c r="E9" s="7" t="inlineStr">
+      <c r="E9" s="8" t="inlineStr">
         <is>
           <t>Administration share</t>
         </is>
       </c>
-      <c r="F9" s="7" t="inlineStr">
+      <c r="F9" s="8" t="inlineStr">
         <is>
           <t>Full cost</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="16" t="inlineStr">
+      <c r="A10" s="17" t="inlineStr">
         <is>
           <t>Housing support (2025)</t>
         </is>
       </c>
-      <c r="B10" s="12" t="n">
+      <c r="B10" s="13" t="n">
         <v>30000</v>
       </c>
-      <c r="C10" s="13">
+      <c r="C10" s="14">
         <f>B10/$B$5</f>
         <v/>
       </c>
-      <c r="D10" s="12">
+      <c r="D10" s="13">
         <f>C10*$B$6</f>
         <v/>
       </c>
-      <c r="E10" s="12">
+      <c r="E10" s="13">
         <f>C10*$B$7</f>
         <v/>
       </c>
-      <c r="F10" s="12">
+      <c r="F10" s="13">
         <f>B10+D10+E10</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="16" t="inlineStr">
+      <c r="A11" s="17" t="inlineStr">
         <is>
           <t>Youth outreach</t>
         </is>
       </c>
-      <c r="B11" s="12" t="n">
+      <c r="B11" s="13" t="n">
         <v>21079</v>
       </c>
-      <c r="C11" s="13">
+      <c r="C11" s="14">
         <f>B11/$B$5</f>
         <v/>
       </c>
-      <c r="D11" s="12">
+      <c r="D11" s="13">
         <f>C11*$B$6</f>
         <v/>
       </c>
-      <c r="E11" s="12">
+      <c r="E11" s="13">
         <f>C11*$B$7</f>
         <v/>
       </c>
-      <c r="F11" s="12">
+      <c r="F11" s="13">
         <f>B11+D11+E11</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="16" t="inlineStr">
+      <c r="A12" s="17" t="inlineStr">
         <is>
           <t>Emergency relief</t>
         </is>
       </c>
-      <c r="B12" s="12" t="n">
+      <c r="B12" s="13" t="n">
         <v>11400</v>
       </c>
-      <c r="C12" s="13">
+      <c r="C12" s="14">
         <f>B12/$B$5</f>
         <v/>
       </c>
-      <c r="D12" s="12">
+      <c r="D12" s="13">
         <f>C12*$B$6</f>
         <v/>
       </c>
-      <c r="E12" s="12">
+      <c r="E12" s="13">
         <f>C12*$B$7</f>
         <v/>
       </c>
-      <c r="F12" s="12">
+      <c r="F12" s="13">
         <f>B12+D12+E12</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="16" t="inlineStr">
+      <c r="A13" s="17" t="inlineStr">
         <is>
           <t>Digital literacy</t>
         </is>
       </c>
-      <c r="B13" s="12" t="n">
+      <c r="B13" s="13" t="n">
         <v>4585</v>
       </c>
-      <c r="C13" s="13">
+      <c r="C13" s="14">
         <f>B13/$B$5</f>
         <v/>
       </c>
-      <c r="D13" s="12">
+      <c r="D13" s="13">
         <f>C13*$B$6</f>
         <v/>
       </c>
-      <c r="E13" s="12">
+      <c r="E13" s="13">
         <f>C13*$B$7</f>
         <v/>
       </c>
-      <c r="F13" s="12">
+      <c r="F13" s="13">
         <f>B13+D13+E13</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="16" t="inlineStr">
+      <c r="A14" s="17" t="inlineStr">
         <is>
           <t>Community meals (2025-26)</t>
         </is>
       </c>
-      <c r="B14" s="12" t="n">
+      <c r="B14" s="13" t="n">
         <v>3100</v>
       </c>
-      <c r="C14" s="13">
+      <c r="C14" s="14">
         <f>B14/$B$5</f>
         <v/>
       </c>
-      <c r="D14" s="12">
+      <c r="D14" s="13">
         <f>C14*$B$6</f>
         <v/>
       </c>
-      <c r="E14" s="12">
+      <c r="E14" s="13">
         <f>C14*$B$7</f>
         <v/>
       </c>
-      <c r="F14" s="12">
+      <c r="F14" s="13">
         <f>B14+D14+E14</f>
         <v/>
       </c>
@@ -1902,7 +1914,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 program-cost.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 program-cost.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 10 Oct 2026, 9:55pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
